--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>115701210</v>
       </c>
       <c r="B3" t="n">
-        <v>57271</v>
+        <v>57484</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>115701210</v>
       </c>
       <c r="B3" t="n">
-        <v>57484</v>
+        <v>57487</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>115701210</v>
       </c>
       <c r="B3" t="n">
-        <v>57487</v>
+        <v>57493</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>115701210</v>
       </c>
       <c r="B3" t="n">
-        <v>57493</v>
+        <v>57496</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -806,7 +806,7 @@
         <v>115701210</v>
       </c>
       <c r="B3" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109778619</v>
+        <v>115701210</v>
       </c>
       <c r="B2" t="n">
-        <v>56632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>100048</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -731,13 +722,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>723253.1602769095</v>
+        <v>723134</v>
       </c>
       <c r="R2" t="n">
-        <v>7056251.524064699</v>
+        <v>7056386</v>
       </c>
       <c r="S2" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,22 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:32</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ropande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,27 +777,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Urban Lundström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Urban Lundström</t>
+          <t>Elias Forsberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115701210</v>
+        <v>109778619</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58238</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,33 +800,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100048</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -855,13 +840,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>723134</v>
+        <v>723253</v>
       </c>
       <c r="R3" t="n">
-        <v>7056386</v>
+        <v>7056252</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,17 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ropande</t>
+          <t>2023-06-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -910,12 +900,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Urban Lundström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Elias Forsberg</t>
+          <t>Urban Lundström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 65043-2023 artfynd.xlsx
+++ b/artfynd/A 65043-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115701210</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,8 +919,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109778619</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>